--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-14T12:50:40.128Z</t>
+    <t>2026-09-14T13:01:10.634Z</t>
   </si>
   <si>
     <t>IG: Trade with the world’s No.1 CFD provider | IG International</t>
